--- a/小包系統報表產生_勝一/台積小包材地點代號對照表.xlsx
+++ b/小包系統報表產生_勝一/台積小包材地點代號對照表.xlsx
@@ -76,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -85,6 +85,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -452,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -461,6 +464,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,6 +498,11 @@
           <t>預設料號2</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>FabPhase</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -518,6 +527,11 @@
       </c>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>FB30</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -542,6 +556,11 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FB30</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -566,6 +585,11 @@
       </c>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>FB30</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -590,6 +614,11 @@
       </c>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>FB30</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -614,6 +643,11 @@
       </c>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>FB30</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -638,6 +672,11 @@
       </c>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>151A</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -662,6 +701,11 @@
       </c>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>151A</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -686,6 +730,11 @@
       </c>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>151A</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -710,6 +759,11 @@
       </c>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>151A</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -734,6 +788,11 @@
       </c>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>151A</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -758,6 +817,11 @@
       </c>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>153A</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -782,6 +846,11 @@
       </c>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>153A</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -806,6 +875,11 @@
       </c>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>153A</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -830,6 +904,11 @@
       </c>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>153A</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -854,6 +933,11 @@
       </c>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>153A</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -878,6 +962,11 @@
       </c>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>155A</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -902,6 +991,11 @@
       </c>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>155A</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -926,6 +1020,11 @@
       </c>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>155A</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -950,6 +1049,11 @@
       </c>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>155A</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -974,6 +1078,11 @@
       </c>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>155A</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -998,6 +1107,11 @@
       </c>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n"/>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>156A</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1022,6 +1136,11 @@
       </c>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n"/>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>156A</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1046,6 +1165,11 @@
       </c>
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n"/>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>156A</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1070,6 +1194,11 @@
       </c>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n"/>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>156A</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1094,6 +1223,11 @@
       </c>
       <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="n"/>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>156A</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1118,6 +1252,11 @@
       </c>
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="n"/>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>201A</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1142,6 +1281,11 @@
       </c>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="n"/>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>201A</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1174,6 +1318,11 @@
           <t>L1400241-T02</t>
         </is>
       </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>201A</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1198,6 +1347,11 @@
       </c>
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="n"/>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>201A</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1222,6 +1376,11 @@
       </c>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n"/>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>201A</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1246,6 +1405,11 @@
       </c>
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="n"/>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>202A</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1270,6 +1434,11 @@
       </c>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n"/>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>202A</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1294,6 +1463,11 @@
       </c>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n"/>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>202A</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1318,6 +1492,11 @@
       </c>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n"/>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>202A</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1342,6 +1521,11 @@
       </c>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="n"/>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>202A</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1366,6 +1550,11 @@
       </c>
       <c r="E37" s="3" t="n"/>
       <c r="F37" s="3" t="n"/>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>145A</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1390,6 +1579,11 @@
       </c>
       <c r="E38" s="3" t="n"/>
       <c r="F38" s="3" t="n"/>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>145A</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1414,6 +1608,11 @@
       </c>
       <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n"/>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>145A</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1438,6 +1637,11 @@
       </c>
       <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="n"/>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>145A</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1462,6 +1666,11 @@
       </c>
       <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="n"/>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>145A</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1486,6 +1695,11 @@
       </c>
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="n"/>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>146A</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1510,6 +1724,11 @@
       </c>
       <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="n"/>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>146A</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1534,6 +1753,11 @@
       </c>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>146A</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1558,6 +1782,11 @@
       </c>
       <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="n"/>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>146A</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1582,6 +1811,11 @@
       </c>
       <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="n"/>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>146A</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1606,6 +1840,11 @@
       </c>
       <c r="E47" s="3" t="n"/>
       <c r="F47" s="3" t="n"/>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>AP71</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1630,6 +1869,11 @@
       </c>
       <c r="E48" s="3" t="n"/>
       <c r="F48" s="3" t="n"/>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>AP71</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1654,6 +1898,11 @@
       </c>
       <c r="E49" s="3" t="n"/>
       <c r="F49" s="3" t="n"/>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>AP71</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1678,6 +1927,11 @@
       </c>
       <c r="E50" s="3" t="n"/>
       <c r="F50" s="3" t="n"/>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>AP71</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1702,6 +1956,11 @@
       </c>
       <c r="E51" s="3" t="n"/>
       <c r="F51" s="3" t="n"/>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>AP71</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1726,6 +1985,11 @@
       </c>
       <c r="E52" s="3" t="n"/>
       <c r="F52" s="3" t="n"/>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>223B</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1750,6 +2014,11 @@
       </c>
       <c r="E53" s="3" t="n"/>
       <c r="F53" s="3" t="n"/>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>223B</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1774,6 +2043,11 @@
       </c>
       <c r="E54" s="3" t="n"/>
       <c r="F54" s="3" t="n"/>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>223B</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1798,6 +2072,11 @@
       </c>
       <c r="E55" s="3" t="n"/>
       <c r="F55" s="3" t="n"/>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>223B</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1822,6 +2101,11 @@
       </c>
       <c r="E56" s="3" t="n"/>
       <c r="F56" s="3" t="n"/>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>223B</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1846,6 +2130,11 @@
       </c>
       <c r="E57" s="3" t="n"/>
       <c r="F57" s="3" t="n"/>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1870,6 +2159,11 @@
       </c>
       <c r="E58" s="3" t="n"/>
       <c r="F58" s="3" t="n"/>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -1894,6 +2188,11 @@
       </c>
       <c r="E59" s="3" t="n"/>
       <c r="F59" s="3" t="n"/>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1918,6 +2217,11 @@
       </c>
       <c r="E60" s="3" t="n"/>
       <c r="F60" s="3" t="n"/>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -1942,6 +2246,11 @@
       </c>
       <c r="E61" s="3" t="n"/>
       <c r="F61" s="3" t="n"/>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1966,6 +2275,11 @@
       </c>
       <c r="E62" s="3" t="n"/>
       <c r="F62" s="3" t="n"/>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>125A</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -1990,6 +2304,11 @@
       </c>
       <c r="E63" s="3" t="n"/>
       <c r="F63" s="3" t="n"/>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>125A</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2014,6 +2333,11 @@
       </c>
       <c r="E64" s="3" t="n"/>
       <c r="F64" s="3" t="n"/>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>125A</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2038,6 +2362,11 @@
       </c>
       <c r="E65" s="3" t="n"/>
       <c r="F65" s="3" t="n"/>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>125A</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2062,6 +2391,11 @@
       </c>
       <c r="E66" s="3" t="n"/>
       <c r="F66" s="3" t="n"/>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>125A</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2086,6 +2420,11 @@
       </c>
       <c r="E67" s="3" t="n"/>
       <c r="F67" s="3" t="n"/>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>F3E0</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2110,6 +2449,11 @@
       </c>
       <c r="E68" s="3" t="n"/>
       <c r="F68" s="3" t="n"/>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>F3E0</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2134,6 +2478,11 @@
       </c>
       <c r="E69" s="3" t="n"/>
       <c r="F69" s="3" t="n"/>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>F3E0</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2158,6 +2507,11 @@
       </c>
       <c r="E70" s="3" t="n"/>
       <c r="F70" s="3" t="n"/>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>F3E0</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2182,6 +2536,11 @@
       </c>
       <c r="E71" s="3" t="n"/>
       <c r="F71" s="3" t="n"/>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>F3E0</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2206,6 +2565,11 @@
       </c>
       <c r="E72" s="3" t="n"/>
       <c r="F72" s="3" t="n"/>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>VISERA</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2230,6 +2594,11 @@
       </c>
       <c r="E73" s="3" t="n"/>
       <c r="F73" s="3" t="n"/>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>VISERA</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2254,6 +2623,11 @@
       </c>
       <c r="E74" s="3" t="n"/>
       <c r="F74" s="3" t="n"/>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>VISERA</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2278,6 +2652,11 @@
       </c>
       <c r="E75" s="3" t="n"/>
       <c r="F75" s="3" t="n"/>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>VISERA</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2302,6 +2681,11 @@
       </c>
       <c r="E76" s="3" t="n"/>
       <c r="F76" s="3" t="n"/>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>VISERA</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2330,6 +2714,11 @@
         </is>
       </c>
       <c r="F77" s="3" t="n"/>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>126A</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2354,6 +2743,11 @@
       </c>
       <c r="E78" s="3" t="n"/>
       <c r="F78" s="3" t="n"/>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>126A</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2378,6 +2772,11 @@
       </c>
       <c r="E79" s="3" t="n"/>
       <c r="F79" s="3" t="n"/>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>126A</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2402,6 +2801,11 @@
       </c>
       <c r="E80" s="3" t="n"/>
       <c r="F80" s="3" t="n"/>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>126A</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2426,6 +2830,11 @@
       </c>
       <c r="E81" s="3" t="n"/>
       <c r="F81" s="3" t="n"/>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>126A</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2450,6 +2859,11 @@
       </c>
       <c r="E82" s="3" t="n"/>
       <c r="F82" s="3" t="n"/>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>128A</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -2478,6 +2892,11 @@
         </is>
       </c>
       <c r="F83" s="3" t="n"/>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>128A</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2502,6 +2921,11 @@
       </c>
       <c r="E84" s="3" t="n"/>
       <c r="F84" s="3" t="n"/>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>128A</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -2526,6 +2950,11 @@
       </c>
       <c r="E85" s="3" t="n"/>
       <c r="F85" s="3" t="n"/>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>128A</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2550,6 +2979,11 @@
       </c>
       <c r="E86" s="3" t="n"/>
       <c r="F86" s="3" t="n"/>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>128A</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -2574,6 +3008,11 @@
       </c>
       <c r="E87" s="3" t="n"/>
       <c r="F87" s="3" t="n"/>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>181A</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2598,6 +3037,11 @@
       </c>
       <c r="E88" s="3" t="n"/>
       <c r="F88" s="3" t="n"/>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>181A</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -2622,6 +3066,11 @@
       </c>
       <c r="E89" s="3" t="n"/>
       <c r="F89" s="3" t="n"/>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>181A</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2650,6 +3099,11 @@
         </is>
       </c>
       <c r="F90" s="3" t="n"/>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>181A</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -2674,6 +3128,11 @@
       </c>
       <c r="E91" s="3" t="n"/>
       <c r="F91" s="3" t="n"/>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>181A</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -2698,6 +3157,11 @@
       </c>
       <c r="E92" s="3" t="n"/>
       <c r="F92" s="3" t="n"/>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>182A</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -2722,6 +3186,11 @@
       </c>
       <c r="E93" s="3" t="n"/>
       <c r="F93" s="3" t="n"/>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>182A</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -2746,6 +3215,11 @@
       </c>
       <c r="E94" s="3" t="n"/>
       <c r="F94" s="3" t="n"/>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>182A</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -2770,6 +3244,11 @@
       </c>
       <c r="E95" s="3" t="n"/>
       <c r="F95" s="3" t="n"/>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>182A</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -2798,6 +3277,11 @@
         </is>
       </c>
       <c r="F96" s="3" t="n"/>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>182A</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -2826,6 +3310,11 @@
         </is>
       </c>
       <c r="F97" s="3" t="n"/>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>183A</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -2854,6 +3343,11 @@
         </is>
       </c>
       <c r="F98" s="3" t="n"/>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>183A</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -2882,6 +3376,11 @@
         </is>
       </c>
       <c r="F99" s="3" t="n"/>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>183A</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -2910,6 +3409,11 @@
         </is>
       </c>
       <c r="F100" s="3" t="n"/>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>183A</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -2938,6 +3442,11 @@
         </is>
       </c>
       <c r="F101" s="3" t="n"/>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>183A</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -2970,6 +3479,11 @@
           <t>L1400241-T02</t>
         </is>
       </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>184A</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -3002,6 +3516,11 @@
           <t>L1400241-T02</t>
         </is>
       </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>184A</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -3034,6 +3553,11 @@
           <t>L1400241-T02</t>
         </is>
       </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>184A</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -3066,6 +3590,11 @@
           <t>L1400241-T02</t>
         </is>
       </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>184A</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -3098,6 +3627,11 @@
           <t>L1400241-T02</t>
         </is>
       </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>184A</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -3130,6 +3664,11 @@
           <t>L1400241-T02</t>
         </is>
       </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>186A</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -3162,6 +3701,11 @@
           <t>L1400241-T02</t>
         </is>
       </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>186A</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -3194,6 +3738,11 @@
           <t>L1400241-T02</t>
         </is>
       </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>186A</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -3226,6 +3775,11 @@
           <t>L1400241-T02</t>
         </is>
       </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>186A</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -3258,6 +3812,11 @@
           <t>L1400241-T02</t>
         </is>
       </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>186A</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -3290,6 +3849,11 @@
           <t>L1400241-T02</t>
         </is>
       </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>187A</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -3322,6 +3886,11 @@
           <t>L1400241-T02</t>
         </is>
       </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>187A</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -3354,6 +3923,11 @@
           <t>L1400241-T02</t>
         </is>
       </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>187A</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -3386,6 +3960,11 @@
           <t>L1400241-T02</t>
         </is>
       </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>187A</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -3418,6 +3997,11 @@
           <t>L1400241-T02</t>
         </is>
       </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>187A</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -3446,6 +4030,11 @@
         </is>
       </c>
       <c r="F117" s="3" t="n"/>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>188A</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -3474,6 +4063,11 @@
         </is>
       </c>
       <c r="F118" s="3" t="n"/>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>188A</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -3502,6 +4096,11 @@
         </is>
       </c>
       <c r="F119" s="3" t="n"/>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>188A</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -3530,6 +4129,11 @@
         </is>
       </c>
       <c r="F120" s="3" t="n"/>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>188A</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -3558,6 +4162,11 @@
         </is>
       </c>
       <c r="F121" s="3" t="n"/>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>188A</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -3586,6 +4195,11 @@
         </is>
       </c>
       <c r="F122" s="3" t="n"/>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>221A</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -3614,6 +4228,11 @@
         </is>
       </c>
       <c r="F123" s="3" t="n"/>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>221A</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -3642,6 +4261,11 @@
         </is>
       </c>
       <c r="F124" s="3" t="n"/>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>221A</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -3670,6 +4294,11 @@
         </is>
       </c>
       <c r="F125" s="3" t="n"/>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>221A</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -3698,6 +4327,11 @@
         </is>
       </c>
       <c r="F126" s="3" t="n"/>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>221A</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -3726,6 +4360,11 @@
         </is>
       </c>
       <c r="F127" s="3" t="n"/>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>221B</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -3754,6 +4393,11 @@
         </is>
       </c>
       <c r="F128" s="3" t="n"/>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>221B</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -3782,6 +4426,11 @@
         </is>
       </c>
       <c r="F129" s="3" t="n"/>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>221B</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -3810,6 +4459,11 @@
         </is>
       </c>
       <c r="F130" s="3" t="n"/>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>221B</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -3838,6 +4492,11 @@
         </is>
       </c>
       <c r="F131" s="3" t="n"/>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>221B</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -3866,6 +4525,11 @@
         </is>
       </c>
       <c r="F132" s="3" t="n"/>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>222A</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -3894,6 +4558,11 @@
         </is>
       </c>
       <c r="F133" s="3" t="n"/>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>222A</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -3922,6 +4591,11 @@
         </is>
       </c>
       <c r="F134" s="3" t="n"/>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>222A</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -3950,6 +4624,11 @@
         </is>
       </c>
       <c r="F135" s="3" t="n"/>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>222A</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -3978,6 +4657,11 @@
         </is>
       </c>
       <c r="F136" s="3" t="n"/>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>222A</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -4006,6 +4690,11 @@
         </is>
       </c>
       <c r="F137" s="3" t="n"/>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>222B</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -4034,6 +4723,11 @@
         </is>
       </c>
       <c r="F138" s="3" t="n"/>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>222B</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -4062,6 +4756,11 @@
         </is>
       </c>
       <c r="F139" s="3" t="n"/>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>222B</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -4090,6 +4789,11 @@
         </is>
       </c>
       <c r="F140" s="3" t="n"/>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>222B</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -4118,6 +4822,11 @@
         </is>
       </c>
       <c r="F141" s="3" t="n"/>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>222B</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
